--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVII/LTAIPT_A63F27.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVII/LTAIPT_A63F27.xlsx
@@ -1,28 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c8ec10a61716621/Documentos/CUARTO PAG WEB/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_470F97C58A52F49DC6A4EDB5654EF2C4CA93F082" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{AD3D90F7-2277-4604-8315-BA7945829532}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
     <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
+    <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_14">Hidden_1!$A$1:$A$7</definedName>
     <definedName name="Hidden_29">Hidden_2!$A$1:$A$3</definedName>
-    <definedName name="Hidden_323">Hidden_3!$A$1:$A$2</definedName>
+    <definedName name="Hidden_314">Hidden_3!$A$1:$A$2</definedName>
+    <definedName name="Hidden_424">Hidden_4!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="95">
   <si>
     <t>48981</t>
   </si>
@@ -105,6 +113,9 @@
     <t>436376</t>
   </si>
   <si>
+    <t>571934</t>
+  </si>
+  <si>
     <t>436382</t>
   </si>
   <si>
@@ -192,6 +203,9 @@
     <t>Razón social del titular al cual se otorgó el acto jurídico</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fecha de inicio de vigencia del acto jurídico </t>
   </si>
   <si>
@@ -237,16 +251,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>B9272FF83F4CCD8735DC7842CC0635A5</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
@@ -255,33 +260,42 @@
     <t>Departamento  de Recursos Humanos</t>
   </si>
   <si>
-    <t>13/01/2023</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no realiza consesiones para ejecución y operación de obra pública,prestación de servicio público , radiodifusión, telcomuniaciones;  no otorga permisos para el tratamiento y refinación del petroleo, almacenamiento, transporte y distribución  de ductos de petróleo, gas, petroliferos y petroquimicos; de radiodifución  de telecomunicación, de ocnducir; no otorga licencias de uso de suelo, de construcción, de anuncios, de conducir, de explotación de yacimientos de materiales pétreos, de explotación  y exracción del petróleo; no autoriza cambios de giro de locales del mercadopúblico, de espectáculos en la vía pública, parques o espacios públicos, de usos y ocupación, del Programa especial de protección civil , de juegos pirotécnicos; para impartir educación, para el accesoa la multiprogramación;  no realiza contratos con cargo total o parcial a recursos públicos; no realiza convenios  para desarrollar un asunto concreo destinado a establecer, transferir, modificar o eliminar  una obligació; debido a que dichos actos jurídicos no se encuentran dentro de sus atribuciones establecidas por ser una Institución Educativa, la cual tiene por objeto, en la esfera de su competencia estatal, impartir, impulsar, coordinar y normar la educación correspondiente al ciclo de nivel medio superior, lo anterior establecido en su Reglamento Interior vigente.</t>
+    <t>AF8EC950F4387A817681F6930DDA516A</t>
+  </si>
+  <si>
+    <t>01/10/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>12/01/2024</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de octubre de 2023 al 31 de diciembre de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no realiza consesiones para ejecución y operación de obra pública,prestación de servicio público , radiodifusión, telcomuniaciones;  no otorga permisos para el tratamiento y refinación del petroleo, almacenamiento, transporte y distribución  de ductos de petróleo, gas, petroliferos y petroquimicos; de radiodifución  de telecomunicación, de ocnducir; no otorga licencias de uso de suelo, de construcción, de anuncios, de conducir, de explotación de yacimientos de materiales pétreos, de explotación  y exracción del petróleo; no autoriza cambios de giro de locales del mercadopúblico, de espectáculos en la vía pública, parques o espacios públicos, de usos y ocupación, del Programa especial de protección civil , de juegos pirotécnicos; para impartir educación, para el accesoa la multiprogramación;  no realiza contratos con cargo total o parcial a recursos públicos; no realiza convenios  para desarrollar un asunto concreo destinado a establecer, transferir, modificar o eliminar  una obligació; debido a que dichos actos jurídicos no se encuentran dentro de sus atribuciones establecidas por ser una Institución Educativa, la cual tiene por objeto, en la esfera de su competencia estatal, impartir, impulsar, coordinar y normar la educación correspondiente al ciclo de nivel medio superior, lo anterior establecido en su Reglamento Interior vigente.</t>
+  </si>
+  <si>
+    <t>Licencia</t>
+  </si>
+  <si>
+    <t>Contrato</t>
+  </si>
+  <si>
+    <t>Convenio</t>
+  </si>
+  <si>
+    <t>Permiso</t>
+  </si>
+  <si>
+    <t>Concesión</t>
+  </si>
+  <si>
+    <t>Autorización</t>
   </si>
   <si>
     <t>Asignaciones</t>
   </si>
   <si>
-    <t>Licencia</t>
-  </si>
-  <si>
-    <t>Contrato</t>
-  </si>
-  <si>
-    <t>Convenio</t>
-  </si>
-  <si>
-    <t>Permiso</t>
-  </si>
-  <si>
-    <t>Concesión</t>
-  </si>
-  <si>
-    <t>Autorización</t>
-  </si>
-  <si>
     <t>Privado</t>
   </si>
   <si>
@@ -289,6 +303,12 @@
   </si>
   <si>
     <t>Mixto</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
   <si>
     <t>Si</t>
@@ -300,7 +320,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -396,6 +416,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -411,44 +434,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -476,14 +499,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -511,6 +551,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -522,175 +579,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -704,29 +737,30 @@
     <col min="12" max="12" width="49.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="51.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="38" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="63.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="55.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="55.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="77.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="61.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="69.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="49.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="49.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="255" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="38" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="63.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="55.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="77.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="69.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -743,7 +777,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -758,7 +792,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -799,25 +833,25 @@
         <v>6</v>
       </c>
       <c r="O4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P4" t="s">
         <v>7</v>
       </c>
       <c r="Q4" t="s">
+        <v>7</v>
+      </c>
+      <c r="R4" t="s">
         <v>6</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>10</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>9</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>11</v>
-      </c>
-      <c r="U4" t="s">
-        <v>10</v>
       </c>
       <c r="V4" t="s">
         <v>10</v>
@@ -826,25 +860,28 @@
         <v>10</v>
       </c>
       <c r="X4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y4" t="s">
         <v>8</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>10</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>9</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>7</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>12</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -929,10 +966,13 @@
       <c r="AC5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -962,185 +1002,192 @@
       <c r="AA6" s="4"/>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
-    </row>
-    <row r="7" spans="1:29" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="AD6" s="4"/>
+    </row>
+    <row r="7" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="AB8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AC6"/>
+    <mergeCell ref="A6:AD6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1148,15 +1195,18 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E197">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E198" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J197">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J198" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Hidden_29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X197">
-      <formula1>Hidden_323</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O8:O198" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>Hidden_314</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y8:Y198" xr:uid="{00000000-0002-0000-0000-000003000000}">
+      <formula1>Hidden_424</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1164,43 +1214,43 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1209,23 +1259,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1234,18 +1284,38 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
